--- a/data-manipulation-scripts/sheets-cleanup/sheets/VARAO FREIO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/VARAO FREIO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -191,7 +191,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -467,7 +467,9 @@
       <c r="C2" s="4">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -501,7 +503,9 @@
       <c r="C3" s="4">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -535,7 +539,9 @@
       <c r="C4" s="7">
         <v>1.0</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -569,7 +575,9 @@
       <c r="C5" s="7">
         <v>1.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -603,7 +611,9 @@
       <c r="C6" s="7">
         <v>1.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="5">
+        <v>30.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -635,7 +645,9 @@
       <c r="C7" s="7">
         <v>1.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5">
+        <v>30.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -669,7 +681,9 @@
       <c r="C8" s="7">
         <v>1.0</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -703,7 +717,9 @@
       <c r="C9" s="7">
         <v>1.0</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -737,7 +753,9 @@
       <c r="C10" s="7">
         <v>1.0</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="5">
+        <v>36.0</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -771,7 +789,9 @@
       <c r="C11" s="7">
         <v>1.0</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -805,7 +825,9 @@
       <c r="C12" s="7">
         <v>9.0</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="5">
+        <v>30.0</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -839,7 +861,9 @@
       <c r="C13" s="7">
         <v>3.0</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="5">
+        <v>30.0</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -873,7 +897,9 @@
       <c r="C14" s="7">
         <v>3.0</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="5">
+        <v>30.0</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -907,7 +933,9 @@
       <c r="C15" s="7">
         <v>5.0</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -977,8 +1005,8 @@
       <c r="C17" s="7">
         <v>5.0</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>4</v>
+      <c r="D17" s="5">
+        <v>25.0</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -1049,7 +1077,9 @@
       <c r="C19" s="7">
         <v>5.0</v>
       </c>
-      <c r="D19" s="6"/>
+      <c r="D19" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -1083,7 +1113,9 @@
       <c r="C20" s="7">
         <v>2.0</v>
       </c>
-      <c r="D20" s="6"/>
+      <c r="D20" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
